--- a/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>CTM</t>
   </si>
@@ -953,7 +953,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="E14" s="3">
         <v>100</v>
@@ -1048,8 +1048,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
+      <c r="D17" s="3">
+        <v>20300</v>
       </c>
       <c r="E17" s="3">
         <v>14400</v>
@@ -1089,8 +1089,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
+      <c r="D18" s="3">
+        <v>-8600</v>
       </c>
       <c r="E18" s="3">
         <v>-1900</v>
@@ -1147,8 +1147,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>400</v>
       </c>
       <c r="E20" s="3">
         <v>600</v>
@@ -1188,8 +1188,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>-7600</v>
       </c>
       <c r="E21" s="3">
         <v>-600</v>
@@ -1270,8 +1270,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
+      <c r="D23" s="3">
+        <v>-9100</v>
       </c>
       <c r="E23" s="3">
         <v>-2100</v>
@@ -1393,8 +1393,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
+      <c r="D26" s="3">
+        <v>-9200</v>
       </c>
       <c r="E26" s="3">
         <v>-2100</v>
@@ -1434,8 +1434,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
+      <c r="D27" s="3">
+        <v>-9200</v>
       </c>
       <c r="E27" s="3">
         <v>-2100</v>
@@ -1639,8 +1639,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
         <v>-600</v>
@@ -1680,8 +1680,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
+      <c r="D33" s="3">
+        <v>-9200</v>
       </c>
       <c r="E33" s="3">
         <v>-2100</v>
@@ -1762,8 +1762,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
+      <c r="D35" s="3">
+        <v>-9200</v>
       </c>
       <c r="E35" s="3">
         <v>-2100</v>
@@ -2574,7 +2574,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5000</v>
+        <v>6900</v>
       </c>
       <c r="E59" s="3">
         <v>5200</v>
@@ -2860,8 +2860,8 @@
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>5</v>
+      <c r="D66" s="3">
+        <v>17700</v>
       </c>
       <c r="E66" s="3">
         <v>17700</v>
@@ -3082,8 +3082,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
+      <c r="D72" s="3">
+        <v>-41800</v>
       </c>
       <c r="E72" s="3">
         <v>-32600</v>
@@ -3246,8 +3246,8 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>5</v>
+      <c r="D76" s="3">
+        <v>13800</v>
       </c>
       <c r="E76" s="3">
         <v>22100</v>
@@ -3374,8 +3374,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
+      <c r="D81" s="3">
+        <v>-9200</v>
       </c>
       <c r="E81" s="3">
         <v>-2100</v>

--- a/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
@@ -656,200 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F8" s="3">
         <v>11700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>12500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>9900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>10000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>11100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>11100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>10000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>9500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>7400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4000</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F9" s="3">
         <v>6900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>7300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>5900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>5900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>6500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>6400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>5900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>5100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>4300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2200</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F10" s="3">
         <v>4800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>5200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>4000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>4100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>4600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>4700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1800</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,8 +890,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,8 +933,14 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,49 +980,61 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F14" s="3">
         <v>6900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1020,17 +1065,23 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>5</v>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,90 +1094,104 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>12600</v>
+      </c>
+      <c r="F17" s="3">
         <v>20300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>14400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>14900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>14300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>13200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>13800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>10800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>11500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>12000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-5000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-4300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-4600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,35 +1207,37 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1183,54 +1250,66 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-7600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-4200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-3800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4200</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-200</v>
       </c>
       <c r="O21" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E22" s="3">
         <v>800</v>
@@ -1239,75 +1318,87 @@
         <v>800</v>
       </c>
       <c r="G22" s="3">
+        <v>800</v>
+      </c>
+      <c r="H22" s="3">
+        <v>800</v>
+      </c>
+      <c r="I22" s="3">
         <v>1400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>1000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>700</v>
-      </c>
-      <c r="L22" s="3">
-        <v>600</v>
-      </c>
-      <c r="M22" s="3">
-        <v>600</v>
       </c>
       <c r="N22" s="3">
         <v>600</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+      <c r="P22" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-9100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-5500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-5800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1315,40 +1406,46 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-1800</v>
-      </c>
-      <c r="L24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-300</v>
       </c>
       <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,90 +1485,108 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-9200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-4300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-5700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-3100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-9200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-4400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-5700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-3100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1626,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1673,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1720,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,35 +1767,41 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -1675,49 +1814,61 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-9200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-4400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-5700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-3100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,95 +1908,113 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-9200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-4400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-5700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-3100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +2030,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,49 +2049,57 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F41" s="3">
         <v>1300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2300</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
       <c r="M41" s="3">
         <v>0</v>
       </c>
       <c r="N41" s="3">
         <v>0</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1960,49 +2139,61 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8400</v>
+        <v>6900</v>
       </c>
       <c r="E43" s="3">
-        <v>7200</v>
+        <v>7000</v>
       </c>
       <c r="F43" s="3">
         <v>8400</v>
       </c>
       <c r="G43" s="3">
+        <v>7200</v>
+      </c>
+      <c r="H43" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I43" s="3">
         <v>5500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>8500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>7700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2028,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="K44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M44" s="3">
         <v>100</v>
@@ -2039,41 +2230,47 @@
       <c r="N44" s="3">
         <v>100</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>100</v>
+      </c>
+      <c r="P44" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>600</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2083,37 +2280,43 @@
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F46" s="3">
         <v>10100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>11400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>10600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8300</v>
-      </c>
-      <c r="K46" s="3">
-        <v>100</v>
-      </c>
-      <c r="L46" s="3">
-        <v>100</v>
       </c>
       <c r="M46" s="3">
         <v>100</v>
@@ -2121,11 +2324,17 @@
       <c r="N46" s="3">
         <v>100</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>100</v>
+      </c>
+      <c r="P46" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2165,79 +2374,91 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>900</v>
+      </c>
+      <c r="F48" s="3">
         <v>1100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1200</v>
-      </c>
-      <c r="F48" s="3">
-        <v>300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>200</v>
       </c>
       <c r="H48" s="3">
         <v>300</v>
       </c>
       <c r="I48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J48" s="3">
         <v>300</v>
       </c>
       <c r="K48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L48" s="3">
+        <v>300</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3">
         <v>100</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3">
         <v>600</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>19700</v>
+      </c>
+      <c r="F49" s="3">
         <v>20300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>27600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>28200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>22200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>22700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>23200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>20900</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>5</v>
       </c>
@@ -2247,8 +2468,14 @@
       <c r="O49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2515,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,16 +2562,22 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -2353,14 +2592,14 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>800</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2370,8 +2609,14 @@
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,49 +2656,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>30100</v>
+      </c>
+      <c r="F54" s="3">
         <v>31500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>39800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>40000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>33000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>33600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>33400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>30300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>700</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2726,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,228 +2745,260 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>800</v>
+      </c>
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F58" s="3">
         <v>8800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1300</v>
-      </c>
-      <c r="K58" s="3">
-        <v>300</v>
-      </c>
-      <c r="L58" s="3">
-        <v>300</v>
       </c>
       <c r="M58" s="3">
         <v>300</v>
       </c>
       <c r="N58" s="3">
+        <v>300</v>
+      </c>
+      <c r="O58" s="3">
+        <v>300</v>
+      </c>
+      <c r="P58" s="3">
         <v>400</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F59" s="3">
         <v>6900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>5100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>4900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>3900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
-      </c>
-      <c r="L59" s="3">
-        <v>200</v>
-      </c>
-      <c r="M59" s="3">
-        <v>300</v>
       </c>
       <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3">
+        <v>300</v>
+      </c>
+      <c r="P59" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F60" s="3">
         <v>16800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>8800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>9400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>8800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
-      </c>
-      <c r="L60" s="3">
-        <v>600</v>
-      </c>
-      <c r="M60" s="3">
-        <v>600</v>
       </c>
       <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>600</v>
+      </c>
+      <c r="P60" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F61" s="3">
         <v>400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>8300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>8000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>10500</v>
-      </c>
-      <c r="K61" s="3">
-        <v>300</v>
-      </c>
-      <c r="L61" s="3">
-        <v>300</v>
       </c>
       <c r="M61" s="3">
         <v>300</v>
       </c>
       <c r="N61" s="3">
+        <v>300</v>
+      </c>
+      <c r="O61" s="3">
+        <v>300</v>
+      </c>
+      <c r="P61" s="3">
         <v>200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>800</v>
+      </c>
+      <c r="F62" s="3">
         <v>500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>600</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
       <c r="H62" s="3">
         <v>0</v>
       </c>
@@ -2717,11 +3008,11 @@
       <c r="J62" s="3">
         <v>0</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>5</v>
@@ -2732,8 +3023,14 @@
       <c r="O62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +3070,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +3117,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,49 +3164,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>17200</v>
+      </c>
+      <c r="F66" s="3">
         <v>17700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>17700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>17100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>15500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>16400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>14300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>15300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>800</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3234,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3277,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3324,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3371,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,49 +3418,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-48100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-41800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-32600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-30400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-26100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-20400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-17200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-12500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-3500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-3400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-3300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1900</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3512,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3559,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,49 +3606,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>12900</v>
+      </c>
+      <c r="F76" s="3">
         <v>13800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>22100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>22900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>17500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>17200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>19100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>15000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-100</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,95 +3700,113 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-9200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-4400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-5700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-3100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,22 +3822,24 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E83" s="3">
         <v>700</v>
       </c>
       <c r="F83" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="G83" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="H83" s="3">
         <v>500</v>
@@ -3454,22 +3851,28 @@
         <v>500</v>
       </c>
       <c r="K83" s="3">
+        <v>500</v>
+      </c>
+      <c r="L83" s="3">
+        <v>500</v>
+      </c>
+      <c r="M83" s="3">
         <v>800</v>
-      </c>
-      <c r="L83" s="3">
-        <v>400</v>
-      </c>
-      <c r="M83" s="3">
-        <v>400</v>
       </c>
       <c r="N83" s="3">
         <v>400</v>
       </c>
       <c r="O83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+      <c r="P83" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3912,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3959,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +4006,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +4053,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +4100,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>900</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,8 +4170,10 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3755,25 +4196,31 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4260,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,8 +4307,14 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3866,37 +4325,43 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>200</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,8 +4377,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3953,8 +4420,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4467,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4514,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,49 +4561,61 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4158,45 +4655,57 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>2800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>CTM</t>
   </si>
@@ -656,131 +656,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E8" s="3">
         <v>11300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10000</v>
-      </c>
-      <c r="J8" s="3">
-        <v>11100</v>
       </c>
       <c r="K8" s="3">
         <v>11100</v>
       </c>
       <c r="L8" s="3">
+        <v>11100</v>
+      </c>
+      <c r="M8" s="3">
         <v>10000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4000</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -788,93 +795,99 @@
         <v>6800</v>
       </c>
       <c r="E9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F9" s="3">
         <v>6500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7300</v>
-      </c>
-      <c r="H9" s="3">
-        <v>5900</v>
       </c>
       <c r="I9" s="3">
         <v>5900</v>
       </c>
       <c r="J9" s="3">
+        <v>5900</v>
+      </c>
+      <c r="K9" s="3">
         <v>6500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2200</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E10" s="3">
         <v>4500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3100</v>
-      </c>
-      <c r="O10" s="3">
-        <v>1800</v>
       </c>
       <c r="P10" s="3">
         <v>1800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +905,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -939,8 +953,11 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,46 +1003,49 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
@@ -1033,8 +1053,11 @@
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1071,8 +1094,8 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>5</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>5</v>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1122,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E17" s="3">
         <v>14800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>20300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4600</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-500</v>
       </c>
       <c r="P18" s="3">
         <v>-500</v>
       </c>
       <c r="Q18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,8 +1242,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1218,29 +1252,29 @@
         <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1256,63 +1290,69 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>500</v>
-      </c>
-      <c r="E22" s="3">
-        <v>800</v>
       </c>
       <c r="F22" s="3">
         <v>800</v>
@@ -1324,22 +1364,22 @@
         <v>800</v>
       </c>
       <c r="I22" s="3">
+        <v>800</v>
+      </c>
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>900</v>
-      </c>
-      <c r="L22" s="3">
-        <v>700</v>
       </c>
       <c r="M22" s="3">
         <v>700</v>
       </c>
       <c r="N22" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O22" s="3">
         <v>600</v>
@@ -1348,57 +1388,63 @@
         <v>600</v>
       </c>
       <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5200</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-1100</v>
       </c>
       <c r="P23" s="3">
         <v>-1100</v>
       </c>
       <c r="Q23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1406,34 +1452,34 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1800</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-300</v>
       </c>
       <c r="O24" s="3">
         <v>-300</v>
@@ -1441,11 +1487,14 @@
       <c r="P24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4900</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-800</v>
       </c>
       <c r="P26" s="3">
         <v>-800</v>
       </c>
       <c r="Q26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4900</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-800</v>
       </c>
       <c r="P27" s="3">
         <v>-800</v>
       </c>
       <c r="Q27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,8 +1840,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1782,29 +1852,29 @@
         <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -1820,55 +1890,61 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4900</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-800</v>
       </c>
       <c r="P33" s="3">
         <v>-800</v>
       </c>
       <c r="Q33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4900</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-800</v>
       </c>
       <c r="P35" s="3">
         <v>-800</v>
       </c>
       <c r="Q35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,41 +2137,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E41" s="3">
         <v>2300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2300</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
       <c r="N41" s="3">
         <v>0</v>
       </c>
@@ -2095,11 +2182,14 @@
       <c r="P41" s="3">
         <v>0</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2145,55 +2235,61 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E43" s="3">
         <v>6900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5800</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2225,7 +2321,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N44" s="3">
         <v>100</v>
@@ -2236,11 +2332,14 @@
       <c r="P44" s="3">
         <v>100</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>100</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2251,29 +2350,29 @@
         <v>600</v>
       </c>
       <c r="F45" s="3">
+        <v>600</v>
+      </c>
+      <c r="G45" s="3">
         <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>700</v>
       </c>
       <c r="H45" s="3">
         <v>700</v>
       </c>
       <c r="I45" s="3">
+        <v>700</v>
+      </c>
+      <c r="J45" s="3">
         <v>600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>300</v>
       </c>
       <c r="K45" s="3">
         <v>300</v>
       </c>
       <c r="L45" s="3">
+        <v>300</v>
+      </c>
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2286,40 +2385,43 @@
       <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E46" s="3">
         <v>9800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8300</v>
-      </c>
-      <c r="M46" s="3">
-        <v>100</v>
       </c>
       <c r="N46" s="3">
         <v>100</v>
@@ -2330,34 +2432,37 @@
       <c r="P46" s="3">
         <v>100</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>100</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2380,31 +2485,34 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>300</v>
       </c>
       <c r="K48" s="3">
         <v>300</v>
@@ -2413,55 +2521,58 @@
         <v>300</v>
       </c>
       <c r="M48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3">
         <v>100</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
       <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3">
         <v>600</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E49" s="3">
         <v>19100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>20300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>27600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>28200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>22200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>20900</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>5</v>
       </c>
@@ -2474,8 +2585,11 @@
       <c r="Q49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,8 +2685,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2598,11 +2718,11 @@
         <v>0</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2785,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E54" s="3">
         <v>30500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>39800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>40000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>30300</v>
-      </c>
-      <c r="M54" s="3">
-        <v>200</v>
       </c>
       <c r="N54" s="3">
         <v>200</v>
       </c>
       <c r="O54" s="3">
+        <v>200</v>
+      </c>
+      <c r="P54" s="3">
         <v>100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>700</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,87 +2877,91 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E57" s="3">
         <v>800</v>
       </c>
       <c r="F57" s="3">
+        <v>800</v>
+      </c>
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1600</v>
       </c>
       <c r="J57" s="3">
         <v>1600</v>
       </c>
       <c r="K57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>700</v>
-      </c>
-      <c r="M57" s="3">
-        <v>200</v>
       </c>
       <c r="N57" s="3">
         <v>200</v>
       </c>
       <c r="O57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E58" s="3">
         <v>2900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2600</v>
       </c>
       <c r="H58" s="3">
         <v>2600</v>
       </c>
       <c r="I58" s="3">
-        <v>2300</v>
+        <v>2600</v>
       </c>
       <c r="J58" s="3">
         <v>2300</v>
       </c>
       <c r="K58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L58" s="3">
         <v>1400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1300</v>
-      </c>
-      <c r="M58" s="3">
-        <v>300</v>
       </c>
       <c r="N58" s="3">
         <v>300</v>
@@ -2836,13 +2970,16 @@
         <v>300</v>
       </c>
       <c r="P58" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q58" s="3">
         <v>400</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2850,81 +2987,84 @@
         <v>4600</v>
       </c>
       <c r="E59" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F59" s="3">
         <v>4500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2900</v>
-      </c>
-      <c r="M59" s="3">
-        <v>200</v>
       </c>
       <c r="N59" s="3">
         <v>200</v>
       </c>
       <c r="O59" s="3">
+        <v>200</v>
+      </c>
+      <c r="P59" s="3">
         <v>300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E60" s="3">
         <v>8300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>700</v>
-      </c>
-      <c r="N60" s="3">
-        <v>600</v>
       </c>
       <c r="O60" s="3">
         <v>600</v>
@@ -2932,43 +3072,46 @@
       <c r="P60" s="3">
         <v>600</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>600</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8400</v>
+        <v>8000</v>
       </c>
       <c r="E61" s="3">
         <v>8400</v>
       </c>
       <c r="F61" s="3">
+        <v>8400</v>
+      </c>
+      <c r="G61" s="3">
         <v>400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8300</v>
-      </c>
-      <c r="H61" s="3">
-        <v>7700</v>
       </c>
       <c r="I61" s="3">
         <v>7700</v>
       </c>
       <c r="J61" s="3">
+        <v>7700</v>
+      </c>
+      <c r="K61" s="3">
         <v>7600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10500</v>
-      </c>
-      <c r="M61" s="3">
-        <v>300</v>
       </c>
       <c r="N61" s="3">
         <v>300</v>
@@ -2977,31 +3120,34 @@
         <v>300</v>
       </c>
       <c r="P61" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q61" s="3">
         <v>200</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>600</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
       <c r="I62" s="3">
         <v>0</v>
       </c>
@@ -3014,8 +3160,8 @@
       <c r="L62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>5</v>
+      <c r="M62" s="3">
+        <v>0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>5</v>
@@ -3029,8 +3175,11 @@
       <c r="Q62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3325,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E66" s="3">
         <v>17600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17200</v>
-      </c>
-      <c r="F66" s="3">
-        <v>17700</v>
       </c>
       <c r="G66" s="3">
         <v>17700</v>
       </c>
       <c r="H66" s="3">
+        <v>17700</v>
+      </c>
+      <c r="I66" s="3">
         <v>17100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1000</v>
-      </c>
-      <c r="N66" s="3">
-        <v>900</v>
       </c>
       <c r="O66" s="3">
         <v>900</v>
       </c>
       <c r="P66" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q66" s="3">
         <v>800</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3595,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-50000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-48100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-44000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-41800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-32600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-30400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-26100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-20400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-17200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-12500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3795,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E76" s="3">
         <v>12800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-900</v>
-      </c>
-      <c r="N76" s="3">
-        <v>-800</v>
       </c>
       <c r="O76" s="3">
         <v>-800</v>
       </c>
       <c r="P76" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q76" s="3">
         <v>-100</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4900</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-800</v>
       </c>
       <c r="P81" s="3">
         <v>-800</v>
       </c>
       <c r="Q81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4022,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3833,7 +4032,7 @@
         <v>600</v>
       </c>
       <c r="E83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F83" s="3">
         <v>700</v>
@@ -3842,7 +4041,7 @@
         <v>700</v>
       </c>
       <c r="H83" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="I83" s="3">
         <v>500</v>
@@ -3857,10 +4056,10 @@
         <v>500</v>
       </c>
       <c r="M83" s="3">
+        <v>500</v>
+      </c>
+      <c r="N83" s="3">
         <v>800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>400</v>
       </c>
       <c r="O83" s="3">
         <v>400</v>
@@ -3869,10 +4068,13 @@
         <v>400</v>
       </c>
       <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>900</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
       <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4392,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4202,25 +4423,28 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,13 +4540,16 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -4331,37 +4561,40 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>400</v>
-      </c>
-      <c r="O94" s="3">
-        <v>200</v>
       </c>
       <c r="P94" s="3">
         <v>200</v>
       </c>
       <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4612,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,55 +4810,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E100" s="3">
         <v>400</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-400</v>
       </c>
       <c r="F100" s="3">
         <v>-400</v>
       </c>
       <c r="G100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4661,51 +4910,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>CTM</t>
   </si>
@@ -656,238 +656,251 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E8" s="3">
         <v>11500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10000</v>
-      </c>
-      <c r="K8" s="3">
-        <v>11100</v>
       </c>
       <c r="L8" s="3">
         <v>11100</v>
       </c>
       <c r="M8" s="3">
+        <v>11100</v>
+      </c>
+      <c r="N8" s="3">
         <v>10000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4000</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="E9" s="3">
         <v>6800</v>
       </c>
       <c r="F9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="G9" s="3">
         <v>6500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7300</v>
-      </c>
-      <c r="I9" s="3">
-        <v>5900</v>
       </c>
       <c r="J9" s="3">
         <v>5900</v>
       </c>
       <c r="K9" s="3">
+        <v>5900</v>
+      </c>
+      <c r="L9" s="3">
         <v>6500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2200</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3100</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1800</v>
       </c>
       <c r="Q10" s="3">
         <v>1800</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,8 +919,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -956,8 +970,11 @@
       <c r="R12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,49 +1023,52 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
-        <v>300</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
@@ -1056,31 +1076,34 @@
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1097,8 +1120,8 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>5</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>5</v>
@@ -1106,8 +1129,11 @@
       <c r="R15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1149,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E17" s="3">
         <v>13100</v>
       </c>
-      <c r="E17" s="3">
-        <v>14800</v>
-      </c>
       <c r="F17" s="3">
-        <v>12600</v>
+        <v>14000</v>
       </c>
       <c r="G17" s="3">
-        <v>20300</v>
+        <v>12800</v>
       </c>
       <c r="H17" s="3">
-        <v>14400</v>
+        <v>13400</v>
       </c>
       <c r="I17" s="3">
-        <v>14900</v>
+        <v>14300</v>
       </c>
       <c r="J17" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K17" s="3">
         <v>14300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1600</v>
       </c>
-      <c r="E18" s="3">
-        <v>-3500</v>
-      </c>
       <c r="F18" s="3">
-        <v>-1500</v>
+        <v>-2700</v>
       </c>
       <c r="G18" s="3">
-        <v>-8600</v>
+        <v>-1700</v>
       </c>
       <c r="H18" s="3">
-        <v>-1900</v>
+        <v>-1700</v>
       </c>
       <c r="I18" s="3">
-        <v>-5000</v>
+        <v>-1800</v>
       </c>
       <c r="J18" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-4300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4600</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-500</v>
       </c>
       <c r="Q18" s="3">
         <v>-500</v>
       </c>
       <c r="R18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,41 +1276,42 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1293,58 +1327,64 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-900</v>
       </c>
-      <c r="E21" s="3">
-        <v>-2800</v>
-      </c>
       <c r="F21" s="3">
-        <v>-900</v>
+        <v>-2000</v>
       </c>
       <c r="G21" s="3">
-        <v>-7600</v>
+        <v>-1000</v>
       </c>
       <c r="H21" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="I21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J21" s="3">
         <v>-4200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1352,10 +1392,10 @@
         <v>200</v>
       </c>
       <c r="E22" s="3">
+        <v>200</v>
+      </c>
+      <c r="F22" s="3">
         <v>500</v>
-      </c>
-      <c r="F22" s="3">
-        <v>800</v>
       </c>
       <c r="G22" s="3">
         <v>800</v>
@@ -1364,25 +1404,25 @@
         <v>800</v>
       </c>
       <c r="I22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>900</v>
-      </c>
-      <c r="M22" s="3">
-        <v>700</v>
       </c>
       <c r="N22" s="3">
         <v>700</v>
       </c>
       <c r="O22" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="P22" s="3">
         <v>600</v>
@@ -1391,98 +1431,104 @@
         <v>600</v>
       </c>
       <c r="R22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5200</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-1100</v>
       </c>
       <c r="Q23" s="3">
         <v>-1100</v>
       </c>
       <c r="R23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="S23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
       </c>
       <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1800</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-300</v>
       </c>
       <c r="P24" s="3">
         <v>-300</v>
@@ -1490,11 +1536,14 @@
       <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1592,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-5700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4900</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-800</v>
       </c>
       <c r="Q26" s="3">
         <v>-800</v>
       </c>
       <c r="R26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-5700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4900</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-800</v>
       </c>
       <c r="Q27" s="3">
         <v>-800</v>
       </c>
       <c r="R27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1751,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1804,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1857,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,41 +1910,44 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>600</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -1893,58 +1963,64 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1900</v>
+        <v>-1300</v>
       </c>
       <c r="E33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2100</v>
       </c>
-      <c r="I33" s="3">
-        <v>-4400</v>
-      </c>
       <c r="J33" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-5700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4900</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-800</v>
       </c>
       <c r="Q33" s="3">
         <v>-800</v>
       </c>
       <c r="R33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2069,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1900</v>
+        <v>-1300</v>
       </c>
       <c r="E35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2100</v>
       </c>
-      <c r="I35" s="3">
-        <v>-4400</v>
-      </c>
       <c r="J35" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-5700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4900</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-800</v>
       </c>
       <c r="Q35" s="3">
         <v>-800</v>
       </c>
       <c r="R35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2203,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,44 +2224,45 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E41" s="3">
         <v>2400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2300</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
@@ -2185,11 +2272,14 @@
       <c r="Q41" s="3">
         <v>0</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2238,81 +2328,87 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E43" s="3">
         <v>6400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5800</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2324,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O44" s="3">
         <v>100</v>
@@ -2335,47 +2431,50 @@
       <c r="Q44" s="3">
         <v>100</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>100</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3">
+        <v>200</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>400</v>
+      </c>
+      <c r="J45" s="3">
+        <v>300</v>
+      </c>
+      <c r="K45" s="3">
         <v>600</v>
-      </c>
-      <c r="E45" s="3">
-        <v>600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>700</v>
-      </c>
-      <c r="I45" s="3">
-        <v>700</v>
-      </c>
-      <c r="J45" s="3">
-        <v>600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>300</v>
       </c>
       <c r="L45" s="3">
         <v>300</v>
       </c>
       <c r="M45" s="3">
+        <v>300</v>
+      </c>
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2388,43 +2487,46 @@
       <c r="R45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E46" s="3">
         <v>9400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8300</v>
-      </c>
-      <c r="N46" s="3">
-        <v>100</v>
       </c>
       <c r="O46" s="3">
         <v>100</v>
@@ -2435,19 +2537,22 @@
       <c r="Q46" s="3">
         <v>100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>100</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>5</v>
+      <c r="E47" s="3">
+        <v>100</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>5</v>
@@ -2464,8 +2569,8 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2488,34 +2593,37 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>200</v>
-      </c>
-      <c r="K48" s="3">
-        <v>300</v>
       </c>
       <c r="L48" s="3">
         <v>300</v>
@@ -2524,58 +2632,61 @@
         <v>300</v>
       </c>
       <c r="N48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3">
         <v>100</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
       <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
         <v>600</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E49" s="3">
         <v>18600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>20300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>27600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>28200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20900</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>5</v>
       </c>
@@ -2588,8 +2699,11 @@
       <c r="R49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2752,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,31 +2805,34 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2721,11 +2841,11 @@
         <v>0</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>800</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2738,8 +2858,11 @@
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,58 +2911,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E54" s="3">
         <v>29500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>39800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>40000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>30300</v>
-      </c>
-      <c r="N54" s="3">
-        <v>200</v>
       </c>
       <c r="O54" s="3">
         <v>200</v>
       </c>
       <c r="P54" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q54" s="3">
         <v>100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>700</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2987,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,8 +3008,9 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2887,84 +3018,87 @@
         <v>1000</v>
       </c>
       <c r="E57" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="F57" s="3">
         <v>800</v>
       </c>
       <c r="G57" s="3">
+        <v>800</v>
+      </c>
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1700</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1600</v>
       </c>
       <c r="K57" s="3">
         <v>1600</v>
       </c>
       <c r="L57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>700</v>
-      </c>
-      <c r="N57" s="3">
-        <v>200</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H58" s="3">
+        <v>11000</v>
+      </c>
+      <c r="I58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
-        <v>2900</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G58" s="3">
-        <v>8800</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2300</v>
       </c>
       <c r="K58" s="3">
         <v>2300</v>
       </c>
       <c r="L58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M58" s="3">
         <v>1400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1300</v>
-      </c>
-      <c r="N58" s="3">
-        <v>300</v>
       </c>
       <c r="O58" s="3">
         <v>300</v>
@@ -2973,63 +3107,69 @@
         <v>300</v>
       </c>
       <c r="Q58" s="3">
+        <v>300</v>
+      </c>
+      <c r="R58" s="3">
         <v>400</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4600</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
-        <v>4600</v>
+        <v>900</v>
       </c>
       <c r="F59" s="3">
-        <v>4500</v>
+        <v>900</v>
       </c>
       <c r="G59" s="3">
-        <v>6900</v>
+        <v>1100</v>
       </c>
       <c r="H59" s="3">
-        <v>5200</v>
+        <v>1600</v>
       </c>
       <c r="I59" s="3">
-        <v>5100</v>
+        <v>1900</v>
       </c>
       <c r="J59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K59" s="3">
         <v>3800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2900</v>
-      </c>
-      <c r="N59" s="3">
-        <v>200</v>
       </c>
       <c r="O59" s="3">
         <v>200</v>
       </c>
       <c r="P59" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q59" s="3">
         <v>300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3037,37 +3177,37 @@
         <v>8400</v>
       </c>
       <c r="E60" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F60" s="3">
         <v>8300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
-      </c>
-      <c r="O60" s="3">
-        <v>600</v>
       </c>
       <c r="P60" s="3">
         <v>600</v>
@@ -3075,46 +3215,49 @@
       <c r="Q60" s="3">
         <v>600</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>600</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>8000</v>
+        <v>8300</v>
       </c>
       <c r="E61" s="3">
-        <v>8400</v>
+        <v>8700</v>
       </c>
       <c r="F61" s="3">
-        <v>8400</v>
+        <v>9100</v>
       </c>
       <c r="G61" s="3">
-        <v>400</v>
+        <v>8800</v>
       </c>
       <c r="H61" s="3">
-        <v>8300</v>
+        <v>900</v>
       </c>
       <c r="I61" s="3">
-        <v>7700</v>
+        <v>8900</v>
       </c>
       <c r="J61" s="3">
         <v>7700</v>
       </c>
       <c r="K61" s="3">
+        <v>7700</v>
+      </c>
+      <c r="L61" s="3">
         <v>7600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10500</v>
-      </c>
-      <c r="N61" s="3">
-        <v>300</v>
       </c>
       <c r="O61" s="3">
         <v>300</v>
@@ -3123,36 +3266,39 @@
         <v>300</v>
       </c>
       <c r="Q61" s="3">
+        <v>300</v>
+      </c>
+      <c r="R61" s="3">
         <v>200</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="F62" s="3">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="G62" s="3">
-        <v>500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3163,8 +3309,8 @@
       <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>5</v>
@@ -3178,8 +3324,11 @@
       <c r="R62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3377,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3430,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,58 +3483,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E66" s="3">
         <v>17400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17200</v>
-      </c>
-      <c r="G66" s="3">
-        <v>17700</v>
       </c>
       <c r="H66" s="3">
         <v>17700</v>
       </c>
       <c r="I66" s="3">
+        <v>17700</v>
+      </c>
+      <c r="J66" s="3">
         <v>17100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1000</v>
-      </c>
-      <c r="O66" s="3">
-        <v>900</v>
       </c>
       <c r="P66" s="3">
         <v>900</v>
       </c>
       <c r="Q66" s="3">
+        <v>900</v>
+      </c>
+      <c r="R66" s="3">
         <v>800</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3559,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3610,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3663,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3716,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,58 +3769,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-51300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-50000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-48100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-44000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-41800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-32600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-30400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-26100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-20400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-17200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-12500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1900</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3875,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3928,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,58 +3981,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E76" s="3">
         <v>12100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-900</v>
-      </c>
-      <c r="O76" s="3">
-        <v>-800</v>
       </c>
       <c r="P76" s="3">
         <v>-800</v>
       </c>
       <c r="Q76" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R76" s="3">
         <v>-100</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4087,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1900</v>
+        <v>-1300</v>
       </c>
       <c r="E81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2100</v>
       </c>
-      <c r="I81" s="3">
-        <v>-4400</v>
-      </c>
       <c r="J81" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-5700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4900</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-800</v>
       </c>
       <c r="Q81" s="3">
         <v>-800</v>
       </c>
       <c r="R81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,31 +4221,32 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>500</v>
@@ -4059,10 +4258,10 @@
         <v>500</v>
       </c>
       <c r="N83" s="3">
+        <v>500</v>
+      </c>
+      <c r="O83" s="3">
         <v>800</v>
-      </c>
-      <c r="O83" s="3">
-        <v>400</v>
       </c>
       <c r="P83" s="3">
         <v>400</v>
@@ -4071,10 +4270,13 @@
         <v>400</v>
       </c>
       <c r="R83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4325,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4378,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4431,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4484,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,8 +4537,11 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4332,49 +4549,52 @@
         <v>700</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>900</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,19 +4613,20 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -4426,25 +4647,28 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4717,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,19 +4770,22 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -4564,37 +4794,40 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>400</v>
-      </c>
-      <c r="P94" s="3">
-        <v>200</v>
       </c>
       <c r="Q94" s="3">
         <v>200</v>
       </c>
       <c r="R94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,31 +4846,32 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4663,8 +4897,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4950,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5003,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,8 +5056,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4822,72 +5068,75 @@
         <v>-500</v>
       </c>
       <c r="E100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F100" s="3">
         <v>400</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-400</v>
       </c>
       <c r="G100" s="3">
         <v>-400</v>
       </c>
       <c r="H100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4913,54 +5162,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>CTM</t>
   </si>
@@ -656,251 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E8" s="3">
         <v>11600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10000</v>
-      </c>
-      <c r="L8" s="3">
-        <v>11100</v>
       </c>
       <c r="M8" s="3">
         <v>11100</v>
       </c>
       <c r="N8" s="3">
+        <v>11100</v>
+      </c>
+      <c r="O8" s="3">
         <v>10000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4000</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E9" s="3">
         <v>6700</v>
-      </c>
-      <c r="E9" s="3">
-        <v>6800</v>
       </c>
       <c r="F9" s="3">
         <v>6800</v>
       </c>
       <c r="G9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="H9" s="3">
         <v>6500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7300</v>
-      </c>
-      <c r="J9" s="3">
-        <v>5900</v>
       </c>
       <c r="K9" s="3">
         <v>5900</v>
       </c>
       <c r="L9" s="3">
+        <v>5900</v>
+      </c>
+      <c r="M9" s="3">
         <v>6500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2200</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E10" s="3">
         <v>5000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3100</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1800</v>
       </c>
       <c r="R10" s="3">
         <v>1800</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -973,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1026,52 +1042,55 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>900</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
@@ -1079,13 +1098,16 @@
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
         <v>600</v>
@@ -1094,7 +1116,7 @@
         <v>600</v>
       </c>
       <c r="G15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H15" s="3">
         <v>700</v>
@@ -1103,11 +1125,11 @@
         <v>700</v>
       </c>
       <c r="J15" s="3">
+        <v>700</v>
+      </c>
+      <c r="K15" s="3">
         <v>500</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1123,8 +1145,8 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>5</v>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>5</v>
@@ -1132,8 +1154,11 @@
       <c r="S15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E17" s="3">
         <v>13000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1700</v>
       </c>
       <c r="H18" s="3">
         <v>-1700</v>
       </c>
       <c r="I18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4600</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-500</v>
       </c>
       <c r="R18" s="3">
         <v>-500</v>
       </c>
       <c r="S18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,44 +1309,45 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1330,61 +1363,67 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1395,37 +1434,37 @@
         <v>200</v>
       </c>
       <c r="F22" s="3">
+        <v>200</v>
+      </c>
+      <c r="G22" s="3">
         <v>500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>800</v>
       </c>
       <c r="H22" s="3">
         <v>800</v>
       </c>
       <c r="I22" s="3">
+        <v>800</v>
+      </c>
+      <c r="J22" s="3">
         <v>1200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>900</v>
-      </c>
-      <c r="N22" s="3">
-        <v>700</v>
       </c>
       <c r="O22" s="3">
         <v>700</v>
       </c>
       <c r="P22" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="Q22" s="3">
         <v>600</v>
@@ -1434,104 +1473,110 @@
         <v>600</v>
       </c>
       <c r="S22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5200</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-1100</v>
       </c>
       <c r="R23" s="3">
         <v>-1100</v>
       </c>
       <c r="S23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="T23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-300</v>
-      </c>
-      <c r="E24" s="3">
-        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>100</v>
       </c>
       <c r="G24" s="3">
+        <v>100</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-1200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1800</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-300</v>
       </c>
       <c r="Q24" s="3">
         <v>-300</v>
@@ -1539,11 +1584,14 @@
       <c r="R24" s="3">
         <v>-300</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4900</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-800</v>
       </c>
       <c r="R26" s="3">
         <v>-800</v>
       </c>
       <c r="S26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4900</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-800</v>
       </c>
       <c r="R27" s="3">
         <v>-800</v>
       </c>
       <c r="S27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1807,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,44 +1979,47 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -1966,61 +2035,67 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4900</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-800</v>
       </c>
       <c r="R33" s="3">
         <v>-800</v>
       </c>
       <c r="S33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4900</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-800</v>
       </c>
       <c r="R35" s="3">
         <v>-800</v>
       </c>
       <c r="S35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,47 +2310,48 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2300</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
       <c r="P41" s="3">
         <v>0</v>
       </c>
@@ -2275,11 +2361,14 @@
       <c r="R41" s="3">
         <v>0</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2331,61 +2420,67 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E43" s="3">
         <v>6100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2410,8 +2505,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2423,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3">
         <v>100</v>
@@ -2434,50 +2529,53 @@
       <c r="R44" s="3">
         <v>100</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>100</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="3">
+        <v>200</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>300</v>
       </c>
       <c r="M45" s="3">
         <v>300</v>
       </c>
       <c r="N45" s="3">
+        <v>300</v>
+      </c>
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2490,46 +2588,49 @@
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E46" s="3">
         <v>9300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8300</v>
-      </c>
-      <c r="O46" s="3">
-        <v>100</v>
       </c>
       <c r="P46" s="3">
         <v>100</v>
@@ -2540,11 +2641,14 @@
       <c r="R46" s="3">
         <v>100</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>100</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2554,8 +2658,8 @@
       <c r="E47" s="3">
         <v>100</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>5</v>
+      <c r="F47" s="3">
+        <v>100</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>5</v>
@@ -2572,8 +2676,8 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2596,37 +2700,40 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>200</v>
-      </c>
-      <c r="L48" s="3">
-        <v>300</v>
       </c>
       <c r="M48" s="3">
         <v>300</v>
@@ -2635,61 +2742,64 @@
         <v>300</v>
       </c>
       <c r="O48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
-      </c>
       <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
         <v>600</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E49" s="3">
         <v>17900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>20300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>27600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>28200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>20900</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>5</v>
       </c>
@@ -2702,8 +2812,11 @@
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,16 +2924,19 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>200</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
+      <c r="E52" s="3">
+        <v>200</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>5</v>
@@ -2834,8 +2953,8 @@
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -2844,11 +2963,11 @@
         <v>0</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>800</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2861,8 +2980,11 @@
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E54" s="3">
         <v>28800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>29500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>31500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>39800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>40000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>30300</v>
-      </c>
-      <c r="O54" s="3">
-        <v>200</v>
       </c>
       <c r="P54" s="3">
         <v>200</v>
       </c>
       <c r="Q54" s="3">
+        <v>200</v>
+      </c>
+      <c r="R54" s="3">
         <v>100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>700</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,66 +3138,70 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E57" s="3">
         <v>1000</v>
       </c>
       <c r="F57" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="G57" s="3">
         <v>800</v>
       </c>
       <c r="H57" s="3">
+        <v>800</v>
+      </c>
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1600</v>
       </c>
       <c r="L57" s="3">
         <v>1600</v>
       </c>
       <c r="M57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>700</v>
-      </c>
-      <c r="O57" s="3">
-        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
       </c>
       <c r="Q57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3100</v>
+        <v>3800</v>
       </c>
       <c r="E58" s="3">
         <v>3100</v>
@@ -3080,28 +3213,28 @@
         <v>3100</v>
       </c>
       <c r="H58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I58" s="3">
         <v>11000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2600</v>
-      </c>
-      <c r="K58" s="3">
-        <v>2300</v>
       </c>
       <c r="L58" s="3">
         <v>2300</v>
       </c>
       <c r="M58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N58" s="3">
         <v>1400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1300</v>
-      </c>
-      <c r="O58" s="3">
-        <v>300</v>
       </c>
       <c r="P58" s="3">
         <v>300</v>
@@ -3110,107 +3243,113 @@
         <v>300</v>
       </c>
       <c r="R58" s="3">
+        <v>300</v>
+      </c>
+      <c r="S58" s="3">
         <v>400</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="3">
         <v>700</v>
-      </c>
-      <c r="E59" s="3">
-        <v>900</v>
       </c>
       <c r="F59" s="3">
         <v>900</v>
       </c>
       <c r="G59" s="3">
+        <v>900</v>
+      </c>
+      <c r="H59" s="3">
         <v>1100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2900</v>
-      </c>
-      <c r="O59" s="3">
-        <v>200</v>
       </c>
       <c r="P59" s="3">
         <v>200</v>
       </c>
       <c r="Q59" s="3">
+        <v>200</v>
+      </c>
+      <c r="R59" s="3">
         <v>300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8400</v>
+        <v>9800</v>
       </c>
       <c r="E60" s="3">
         <v>8400</v>
       </c>
       <c r="F60" s="3">
+        <v>8400</v>
+      </c>
+      <c r="G60" s="3">
         <v>8300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>700</v>
-      </c>
-      <c r="P60" s="3">
-        <v>600</v>
       </c>
       <c r="Q60" s="3">
         <v>600</v>
@@ -3218,49 +3357,52 @@
       <c r="R60" s="3">
         <v>600</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>600</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E61" s="3">
         <v>8300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8900</v>
-      </c>
-      <c r="J61" s="3">
-        <v>7700</v>
       </c>
       <c r="K61" s="3">
         <v>7700</v>
       </c>
       <c r="L61" s="3">
+        <v>7700</v>
+      </c>
+      <c r="M61" s="3">
         <v>7600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10500</v>
-      </c>
-      <c r="O61" s="3">
-        <v>300</v>
       </c>
       <c r="P61" s="3">
         <v>300</v>
@@ -3269,30 +3411,33 @@
         <v>300</v>
       </c>
       <c r="R61" s="3">
+        <v>300</v>
+      </c>
+      <c r="S61" s="3">
         <v>200</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
         <v>200</v>
       </c>
       <c r="F62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G62" s="3">
         <v>300</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>5</v>
+      <c r="H62" s="3">
+        <v>300</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>5</v>
@@ -3300,8 +3445,8 @@
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -3312,8 +3457,8 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
+      <c r="O62" s="3">
+        <v>0</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>5</v>
@@ -3327,8 +3472,11 @@
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E66" s="3">
         <v>16800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17200</v>
-      </c>
-      <c r="H66" s="3">
-        <v>17700</v>
       </c>
       <c r="I66" s="3">
         <v>17700</v>
       </c>
       <c r="J66" s="3">
+        <v>17700</v>
+      </c>
+      <c r="K66" s="3">
         <v>17100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1000</v>
-      </c>
-      <c r="P66" s="3">
-        <v>900</v>
       </c>
       <c r="Q66" s="3">
         <v>900</v>
       </c>
       <c r="R66" s="3">
+        <v>900</v>
+      </c>
+      <c r="S66" s="3">
         <v>800</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3719,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-54100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-51300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-50000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-48100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-44000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-41800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-32600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-30400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-26100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-20400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-17200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-12500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1900</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E76" s="3">
         <v>12000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-900</v>
-      </c>
-      <c r="P76" s="3">
-        <v>-800</v>
       </c>
       <c r="Q76" s="3">
         <v>-800</v>
       </c>
       <c r="R76" s="3">
+        <v>-800</v>
+      </c>
+      <c r="S76" s="3">
         <v>-100</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4900</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-800</v>
       </c>
       <c r="R81" s="3">
         <v>-800</v>
       </c>
       <c r="S81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,8 +4419,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4249,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
         <v>500</v>
@@ -4261,10 +4459,10 @@
         <v>500</v>
       </c>
       <c r="O83" s="3">
+        <v>500</v>
+      </c>
+      <c r="P83" s="3">
         <v>800</v>
-      </c>
-      <c r="P83" s="3">
-        <v>400</v>
       </c>
       <c r="Q83" s="3">
         <v>400</v>
@@ -4273,10 +4471,13 @@
         <v>400</v>
       </c>
       <c r="S83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>700</v>
+        <v>-400</v>
       </c>
       <c r="E89" s="3">
         <v>700</v>
       </c>
       <c r="F89" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>900</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,22 +4833,23 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>5</v>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -4650,25 +4870,28 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,22 +4999,25 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>200</v>
+      </c>
+      <c r="E94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -4797,37 +5026,40 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-400</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>400</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>200</v>
       </c>
       <c r="R94" s="3">
         <v>200</v>
       </c>
       <c r="S94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4873,8 +5106,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4900,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,61 +5301,67 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-500</v>
+        <v>9700</v>
       </c>
       <c r="E100" s="3">
         <v>-500</v>
       </c>
       <c r="F100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G100" s="3">
         <v>400</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-400</v>
       </c>
       <c r="H100" s="3">
         <v>-400</v>
       </c>
       <c r="I100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5138,8 +5386,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -5165,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>CTM</t>
   </si>
@@ -656,263 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E8" s="3">
         <v>10300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10000</v>
-      </c>
-      <c r="M8" s="3">
-        <v>11100</v>
       </c>
       <c r="N8" s="3">
         <v>11100</v>
       </c>
       <c r="O8" s="3">
+        <v>11100</v>
+      </c>
+      <c r="P8" s="3">
         <v>10000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4000</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E9" s="3">
         <v>6200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6700</v>
-      </c>
-      <c r="F9" s="3">
-        <v>6800</v>
       </c>
       <c r="G9" s="3">
         <v>6800</v>
       </c>
       <c r="H9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I9" s="3">
         <v>6500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7300</v>
-      </c>
-      <c r="K9" s="3">
-        <v>5900</v>
       </c>
       <c r="L9" s="3">
         <v>5900</v>
       </c>
       <c r="M9" s="3">
+        <v>5900</v>
+      </c>
+      <c r="N9" s="3">
         <v>6500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2200</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E10" s="3">
         <v>4100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3100</v>
-      </c>
-      <c r="R10" s="3">
-        <v>1800</v>
       </c>
       <c r="S10" s="3">
         <v>1800</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,55 +1062,58 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>900</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
@@ -1101,16 +1121,19 @@
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>400</v>
+      </c>
+      <c r="E15" s="3">
         <v>500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>600</v>
       </c>
       <c r="F15" s="3">
         <v>600</v>
@@ -1119,7 +1142,7 @@
         <v>600</v>
       </c>
       <c r="H15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I15" s="3">
         <v>700</v>
@@ -1128,11 +1151,11 @@
         <v>700</v>
       </c>
       <c r="K15" s="3">
+        <v>700</v>
+      </c>
+      <c r="L15" s="3">
         <v>500</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1148,8 +1171,8 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>5</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>5</v>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E17" s="3">
         <v>11900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-1700</v>
       </c>
       <c r="I18" s="3">
         <v>-1700</v>
       </c>
       <c r="J18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-1800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4600</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-500</v>
       </c>
       <c r="S18" s="3">
         <v>-500</v>
       </c>
       <c r="T18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="U18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,47 +1343,48 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1366,69 +1400,75 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>200</v>
@@ -1437,37 +1477,37 @@
         <v>200</v>
       </c>
       <c r="G22" s="3">
+        <v>200</v>
+      </c>
+      <c r="H22" s="3">
         <v>500</v>
-      </c>
-      <c r="H22" s="3">
-        <v>800</v>
       </c>
       <c r="I22" s="3">
         <v>800</v>
       </c>
       <c r="J22" s="3">
+        <v>800</v>
+      </c>
+      <c r="K22" s="3">
         <v>1200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>900</v>
-      </c>
-      <c r="O22" s="3">
-        <v>700</v>
       </c>
       <c r="P22" s="3">
         <v>700</v>
       </c>
       <c r="Q22" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="R22" s="3">
         <v>600</v>
@@ -1476,66 +1516,72 @@
         <v>600</v>
       </c>
       <c r="T22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5200</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-1100</v>
       </c>
       <c r="S23" s="3">
         <v>-1100</v>
       </c>
       <c r="T23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1543,43 +1589,43 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-300</v>
-      </c>
-      <c r="F24" s="3">
-        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
       </c>
       <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1800</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>-300</v>
       </c>
       <c r="R24" s="3">
         <v>-300</v>
@@ -1587,11 +1633,14 @@
       <c r="S24" s="3">
         <v>-300</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4900</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-800</v>
       </c>
       <c r="S26" s="3">
         <v>-800</v>
       </c>
       <c r="T26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4900</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-800</v>
       </c>
       <c r="S27" s="3">
         <v>-800</v>
       </c>
       <c r="T27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,47 +2049,50 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2038,64 +2108,70 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4900</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-800</v>
       </c>
       <c r="S33" s="3">
         <v>-800</v>
       </c>
       <c r="T33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4900</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-800</v>
       </c>
       <c r="S35" s="3">
         <v>-800</v>
       </c>
       <c r="T35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,50 +2397,51 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E41" s="3">
         <v>12000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2300</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
       <c r="Q41" s="3">
         <v>0</v>
       </c>
@@ -2364,11 +2451,14 @@
       <c r="S41" s="3">
         <v>0</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,64 +2513,70 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E43" s="3">
         <v>5800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5800</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2508,8 +2604,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2521,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3">
         <v>100</v>
@@ -2532,53 +2628,56 @@
       <c r="S44" s="3">
         <v>100</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>100</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
-      </c>
-      <c r="M45" s="3">
-        <v>300</v>
       </c>
       <c r="N45" s="3">
         <v>300</v>
       </c>
       <c r="O45" s="3">
+        <v>300</v>
+      </c>
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2591,49 +2690,52 @@
       <c r="T45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E46" s="3">
         <v>18900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8300</v>
-      </c>
-      <c r="P46" s="3">
-        <v>100</v>
       </c>
       <c r="Q46" s="3">
         <v>100</v>
@@ -2644,11 +2746,14 @@
       <c r="S46" s="3">
         <v>100</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>100</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2661,8 +2766,8 @@
       <c r="F47" s="3">
         <v>100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>5</v>
+      <c r="G47" s="3">
+        <v>100</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>5</v>
@@ -2679,8 +2784,8 @@
       <c r="L47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2703,8 +2808,11 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2712,31 +2820,31 @@
         <v>1200</v>
       </c>
       <c r="E48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>200</v>
-      </c>
-      <c r="M48" s="3">
-        <v>300</v>
       </c>
       <c r="N48" s="3">
         <v>300</v>
@@ -2745,64 +2853,67 @@
         <v>300</v>
       </c>
       <c r="P48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+      <c r="R48" s="3">
         <v>100</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
-      </c>
       <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
         <v>600</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E49" s="3">
         <v>17500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>20300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>27600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>28200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>23200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>20900</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>5</v>
       </c>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,19 +3044,22 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
+      <c r="F52" s="3">
+        <v>200</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>5</v>
@@ -2956,8 +3076,8 @@
       <c r="K52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2966,11 +3086,11 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>800</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E54" s="3">
         <v>37800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>28800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>29500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>31500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>39800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>40000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>30300</v>
-      </c>
-      <c r="P54" s="3">
-        <v>200</v>
       </c>
       <c r="Q54" s="3">
         <v>200</v>
       </c>
       <c r="R54" s="3">
+        <v>200</v>
+      </c>
+      <c r="S54" s="3">
         <v>100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>700</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,72 +3269,76 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
-      </c>
-      <c r="E57" s="3">
-        <v>1000</v>
       </c>
       <c r="F57" s="3">
         <v>1000</v>
       </c>
       <c r="G57" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H57" s="3">
         <v>800</v>
       </c>
       <c r="I57" s="3">
+        <v>800</v>
+      </c>
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1600</v>
       </c>
       <c r="M57" s="3">
         <v>1600</v>
       </c>
       <c r="N57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>700</v>
-      </c>
-      <c r="P57" s="3">
-        <v>200</v>
       </c>
       <c r="Q57" s="3">
         <v>200</v>
       </c>
       <c r="R57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E58" s="3">
         <v>3800</v>
-      </c>
-      <c r="E58" s="3">
-        <v>3100</v>
       </c>
       <c r="F58" s="3">
         <v>3100</v>
@@ -3216,28 +3350,28 @@
         <v>3100</v>
       </c>
       <c r="I58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J58" s="3">
         <v>11000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2600</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2300</v>
       </c>
       <c r="M58" s="3">
         <v>2300</v>
       </c>
       <c r="N58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O58" s="3">
         <v>1400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1300</v>
-      </c>
-      <c r="P58" s="3">
-        <v>300</v>
       </c>
       <c r="Q58" s="3">
         <v>300</v>
@@ -3246,113 +3380,119 @@
         <v>300</v>
       </c>
       <c r="S58" s="3">
+        <v>300</v>
+      </c>
+      <c r="T58" s="3">
         <v>400</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>700</v>
-      </c>
-      <c r="F59" s="3">
-        <v>900</v>
       </c>
       <c r="G59" s="3">
         <v>900</v>
       </c>
       <c r="H59" s="3">
+        <v>900</v>
+      </c>
+      <c r="I59" s="3">
         <v>1100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2900</v>
-      </c>
-      <c r="P59" s="3">
-        <v>200</v>
       </c>
       <c r="Q59" s="3">
         <v>200</v>
       </c>
       <c r="R59" s="3">
+        <v>200</v>
+      </c>
+      <c r="S59" s="3">
         <v>300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E60" s="3">
         <v>9800</v>
-      </c>
-      <c r="E60" s="3">
-        <v>8400</v>
       </c>
       <c r="F60" s="3">
         <v>8400</v>
       </c>
       <c r="G60" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H60" s="3">
         <v>8300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>700</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>600</v>
       </c>
       <c r="R60" s="3">
         <v>600</v>
@@ -3360,52 +3500,55 @@
       <c r="S60" s="3">
         <v>600</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>600</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E61" s="3">
         <v>7700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8900</v>
-      </c>
-      <c r="K61" s="3">
-        <v>7700</v>
       </c>
       <c r="L61" s="3">
         <v>7700</v>
       </c>
       <c r="M61" s="3">
+        <v>7700</v>
+      </c>
+      <c r="N61" s="3">
         <v>7600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10500</v>
-      </c>
-      <c r="P61" s="3">
-        <v>300</v>
       </c>
       <c r="Q61" s="3">
         <v>300</v>
@@ -3414,33 +3557,36 @@
         <v>300</v>
       </c>
       <c r="S61" s="3">
+        <v>300</v>
+      </c>
+      <c r="T61" s="3">
         <v>200</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>200</v>
       </c>
       <c r="F62" s="3">
         <v>200</v>
       </c>
       <c r="G62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H62" s="3">
         <v>300</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
+      <c r="I62" s="3">
+        <v>300</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
@@ -3448,8 +3594,8 @@
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -3460,8 +3606,8 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
+      <c r="P62" s="3">
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>5</v>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E66" s="3">
         <v>17700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17200</v>
-      </c>
-      <c r="I66" s="3">
-        <v>17700</v>
       </c>
       <c r="J66" s="3">
         <v>17700</v>
       </c>
       <c r="K66" s="3">
+        <v>17700</v>
+      </c>
+      <c r="L66" s="3">
         <v>17100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>900</v>
       </c>
       <c r="R66" s="3">
         <v>900</v>
       </c>
       <c r="S66" s="3">
+        <v>900</v>
+      </c>
+      <c r="T66" s="3">
         <v>800</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-54100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-51300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-50000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-48100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-44000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-41800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-32600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-30400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-26100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-20400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-17200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-12500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1900</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E76" s="3">
         <v>20200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-900</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>-800</v>
       </c>
       <c r="R76" s="3">
         <v>-800</v>
       </c>
       <c r="S76" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T76" s="3">
         <v>-100</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4900</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-800</v>
       </c>
       <c r="S81" s="3">
         <v>-800</v>
       </c>
       <c r="T81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4450,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>500</v>
@@ -4462,10 +4661,10 @@
         <v>500</v>
       </c>
       <c r="P83" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q83" s="3">
         <v>800</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>400</v>
       </c>
       <c r="R83" s="3">
         <v>400</v>
@@ -4474,10 +4673,13 @@
         <v>400</v>
       </c>
       <c r="T83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-400</v>
-      </c>
-      <c r="E89" s="3">
-        <v>700</v>
       </c>
       <c r="F89" s="3">
         <v>700</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>900</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,25 +5054,26 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>5</v>
+      <c r="F91" s="3">
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -4873,25 +5094,28 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,25 +5229,28 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I94" s="3">
         <v>0</v>
@@ -5029,37 +5259,40 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>400</v>
-      </c>
-      <c r="R94" s="3">
-        <v>200</v>
       </c>
       <c r="S94" s="3">
         <v>200</v>
       </c>
       <c r="T94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5109,8 +5343,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5547,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E100" s="3">
         <v>9700</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-500</v>
       </c>
       <c r="F100" s="3">
         <v>-500</v>
       </c>
       <c r="G100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H100" s="3">
         <v>400</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-400</v>
       </c>
       <c r="I100" s="3">
         <v>-400</v>
       </c>
       <c r="J100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5389,8 +5638,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5416,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E102" s="3">
         <v>9500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
   <si>
     <t>CTM</t>
   </si>
@@ -656,276 +656,289 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E8" s="3">
         <v>11700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10000</v>
-      </c>
-      <c r="N8" s="3">
-        <v>11100</v>
       </c>
       <c r="O8" s="3">
         <v>11100</v>
       </c>
       <c r="P8" s="3">
+        <v>11100</v>
+      </c>
+      <c r="Q8" s="3">
         <v>10000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4000</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E9" s="3">
         <v>7100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6700</v>
-      </c>
-      <c r="G9" s="3">
-        <v>6800</v>
       </c>
       <c r="H9" s="3">
         <v>6800</v>
       </c>
       <c r="I9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J9" s="3">
         <v>6500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7300</v>
-      </c>
-      <c r="L9" s="3">
-        <v>5900</v>
       </c>
       <c r="M9" s="3">
         <v>5900</v>
       </c>
       <c r="N9" s="3">
+        <v>5900</v>
+      </c>
+      <c r="O9" s="3">
         <v>6500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2200</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E10" s="3">
         <v>4600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3100</v>
-      </c>
-      <c r="S10" s="3">
-        <v>1800</v>
       </c>
       <c r="T10" s="3">
         <v>1800</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="U10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,8 +960,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,58 +1082,61 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>900</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
@@ -1124,8 +1144,11 @@
       <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1133,10 +1156,10 @@
         <v>400</v>
       </c>
       <c r="E15" s="3">
+        <v>400</v>
+      </c>
+      <c r="F15" s="3">
         <v>500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>600</v>
       </c>
       <c r="G15" s="3">
         <v>600</v>
@@ -1145,7 +1168,7 @@
         <v>600</v>
       </c>
       <c r="I15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="J15" s="3">
         <v>700</v>
@@ -1154,11 +1177,11 @@
         <v>700</v>
       </c>
       <c r="L15" s="3">
+        <v>700</v>
+      </c>
+      <c r="M15" s="3">
         <v>500</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1174,8 +1197,8 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>5</v>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E17" s="3">
         <v>13200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1700</v>
       </c>
       <c r="J18" s="3">
         <v>-1700</v>
       </c>
       <c r="K18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L18" s="3">
         <v>-1800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4600</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-500</v>
       </c>
       <c r="T18" s="3">
         <v>-500</v>
       </c>
       <c r="U18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,50 +1377,51 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1403,67 +1437,73 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>-600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1471,7 +1511,7 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
         <v>200</v>
@@ -1480,37 +1520,37 @@
         <v>200</v>
       </c>
       <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
         <v>500</v>
-      </c>
-      <c r="I22" s="3">
-        <v>800</v>
       </c>
       <c r="J22" s="3">
         <v>800</v>
       </c>
       <c r="K22" s="3">
+        <v>800</v>
+      </c>
+      <c r="L22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>900</v>
-      </c>
-      <c r="P22" s="3">
-        <v>700</v>
       </c>
       <c r="Q22" s="3">
         <v>700</v>
       </c>
       <c r="R22" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="S22" s="3">
         <v>600</v>
@@ -1519,116 +1559,122 @@
         <v>600</v>
       </c>
       <c r="U22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5200</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-1100</v>
       </c>
       <c r="T23" s="3">
         <v>-1100</v>
       </c>
       <c r="U23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
         <v>100</v>
       </c>
       <c r="F24" s="3">
+        <v>100</v>
+      </c>
+      <c r="G24" s="3">
         <v>-300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>100</v>
       </c>
       <c r="I24" s="3">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1800</v>
-      </c>
-      <c r="R24" s="3">
-        <v>-300</v>
       </c>
       <c r="S24" s="3">
         <v>-300</v>
@@ -1636,11 +1682,14 @@
       <c r="T24" s="3">
         <v>-300</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4900</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-800</v>
       </c>
       <c r="T26" s="3">
         <v>-800</v>
       </c>
       <c r="U26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4900</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-800</v>
       </c>
       <c r="T27" s="3">
         <v>-800</v>
       </c>
       <c r="U27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,50 +2119,53 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2111,67 +2181,73 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4900</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-800</v>
       </c>
       <c r="T33" s="3">
         <v>-800</v>
       </c>
       <c r="U33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4900</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-800</v>
       </c>
       <c r="T35" s="3">
         <v>-800</v>
       </c>
       <c r="U35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,53 +2484,54 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E41" s="3">
         <v>13300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2300</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
       <c r="R41" s="3">
         <v>0</v>
       </c>
@@ -2454,11 +2541,14 @@
       <c r="T41" s="3">
         <v>0</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,67 +2606,73 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E43" s="3">
         <v>8700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5800</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2607,8 +2703,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2620,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="Q44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R44" s="3">
         <v>100</v>
@@ -2631,56 +2727,59 @@
       <c r="T44" s="3">
         <v>100</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>100</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
-      </c>
-      <c r="N45" s="3">
-        <v>300</v>
       </c>
       <c r="O45" s="3">
         <v>300</v>
       </c>
       <c r="P45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2693,52 +2792,55 @@
       <c r="U45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E46" s="3">
         <v>22700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8300</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>100</v>
       </c>
       <c r="R46" s="3">
         <v>100</v>
@@ -2749,11 +2851,14 @@
       <c r="T46" s="3">
         <v>100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>100</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2769,8 +2874,8 @@
       <c r="G47" s="3">
         <v>100</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>5</v>
+      <c r="H47" s="3">
+        <v>100</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>5</v>
@@ -2787,8 +2892,8 @@
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2811,8 +2916,11 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2823,31 +2931,31 @@
         <v>1200</v>
       </c>
       <c r="F48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G48" s="3">
         <v>1300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>200</v>
-      </c>
-      <c r="N48" s="3">
-        <v>300</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
@@ -2856,67 +2964,70 @@
         <v>300</v>
       </c>
       <c r="Q48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
         <v>100</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
       <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3">
         <v>600</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E49" s="3">
         <v>17100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>20300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>27600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>28200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>22200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>22700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>23200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>20900</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>5</v>
       </c>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3164,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3056,13 +3176,13 @@
         <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>5</v>
+      <c r="G52" s="3">
+        <v>200</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>5</v>
@@ -3079,8 +3199,8 @@
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3089,11 +3209,11 @@
         <v>0</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>800</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3106,8 +3226,11 @@
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3288,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E54" s="3">
         <v>41100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>28800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>31500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>39800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>40000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>30300</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>200</v>
       </c>
       <c r="R54" s="3">
         <v>200</v>
       </c>
       <c r="S54" s="3">
+        <v>200</v>
+      </c>
+      <c r="T54" s="3">
         <v>100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>700</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,78 +3400,82 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1100</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1000</v>
       </c>
       <c r="G57" s="3">
         <v>1000</v>
       </c>
       <c r="H57" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="I57" s="3">
         <v>800</v>
       </c>
       <c r="J57" s="3">
+        <v>800</v>
+      </c>
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1600</v>
       </c>
       <c r="N57" s="3">
         <v>1600</v>
       </c>
       <c r="O57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>700</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>200</v>
       </c>
       <c r="R57" s="3">
         <v>200</v>
       </c>
       <c r="S57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>3100</v>
       </c>
       <c r="G58" s="3">
         <v>3100</v>
@@ -3353,28 +3487,28 @@
         <v>3100</v>
       </c>
       <c r="J58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K58" s="3">
         <v>11000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2600</v>
-      </c>
-      <c r="M58" s="3">
-        <v>2300</v>
       </c>
       <c r="N58" s="3">
         <v>2300</v>
       </c>
       <c r="O58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P58" s="3">
         <v>1400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1300</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>300</v>
       </c>
       <c r="R58" s="3">
         <v>300</v>
@@ -3383,119 +3517,125 @@
         <v>300</v>
       </c>
       <c r="T58" s="3">
+        <v>300</v>
+      </c>
+      <c r="U58" s="3">
         <v>400</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>700</v>
-      </c>
-      <c r="G59" s="3">
-        <v>900</v>
       </c>
       <c r="H59" s="3">
         <v>900</v>
       </c>
       <c r="I59" s="3">
+        <v>900</v>
+      </c>
+      <c r="J59" s="3">
         <v>1100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2900</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>200</v>
       </c>
       <c r="R59" s="3">
         <v>200</v>
       </c>
       <c r="S59" s="3">
+        <v>200</v>
+      </c>
+      <c r="T59" s="3">
         <v>300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>200</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9800</v>
-      </c>
-      <c r="F60" s="3">
-        <v>8400</v>
       </c>
       <c r="G60" s="3">
         <v>8400</v>
       </c>
       <c r="H60" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I60" s="3">
         <v>8300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>700</v>
-      </c>
-      <c r="R60" s="3">
-        <v>600</v>
       </c>
       <c r="S60" s="3">
         <v>600</v>
@@ -3503,55 +3643,58 @@
       <c r="T60" s="3">
         <v>600</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>600</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E61" s="3">
         <v>7200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8900</v>
-      </c>
-      <c r="L61" s="3">
-        <v>7700</v>
       </c>
       <c r="M61" s="3">
         <v>7700</v>
       </c>
       <c r="N61" s="3">
+        <v>7700</v>
+      </c>
+      <c r="O61" s="3">
         <v>7600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10500</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>300</v>
       </c>
       <c r="R61" s="3">
         <v>300</v>
@@ -3560,36 +3703,39 @@
         <v>300</v>
       </c>
       <c r="T61" s="3">
+        <v>300</v>
+      </c>
+      <c r="U61" s="3">
         <v>200</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
         <v>100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>200</v>
       </c>
       <c r="G62" s="3">
         <v>200</v>
       </c>
       <c r="H62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I62" s="3">
         <v>300</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
+      <c r="J62" s="3">
+        <v>300</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>5</v>
@@ -3597,8 +3743,8 @@
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -3609,8 +3755,8 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>5</v>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3956,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E66" s="3">
         <v>15000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17200</v>
-      </c>
-      <c r="J66" s="3">
-        <v>17700</v>
       </c>
       <c r="K66" s="3">
         <v>17700</v>
       </c>
       <c r="L66" s="3">
+        <v>17700</v>
+      </c>
+      <c r="M66" s="3">
         <v>17100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1000</v>
-      </c>
-      <c r="R66" s="3">
-        <v>900</v>
       </c>
       <c r="S66" s="3">
         <v>900</v>
       </c>
       <c r="T66" s="3">
+        <v>900</v>
+      </c>
+      <c r="U66" s="3">
         <v>800</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4290,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-55600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-55300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-54100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-51300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-50000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-48100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-44000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-41800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-32600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-30400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-26100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-20400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-17200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1900</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4538,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E76" s="3">
         <v>26100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-900</v>
-      </c>
-      <c r="R76" s="3">
-        <v>-800</v>
       </c>
       <c r="S76" s="3">
         <v>-800</v>
       </c>
       <c r="T76" s="3">
+        <v>-800</v>
+      </c>
+      <c r="U76" s="3">
         <v>-100</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4900</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-800</v>
       </c>
       <c r="T81" s="3">
         <v>-800</v>
       </c>
       <c r="U81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4817,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4652,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
         <v>500</v>
@@ -4664,10 +4863,10 @@
         <v>500</v>
       </c>
       <c r="Q83" s="3">
+        <v>500</v>
+      </c>
+      <c r="R83" s="3">
         <v>800</v>
-      </c>
-      <c r="R83" s="3">
-        <v>400</v>
       </c>
       <c r="S83" s="3">
         <v>400</v>
@@ -4676,10 +4875,13 @@
         <v>400</v>
       </c>
       <c r="U83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-400</v>
-      </c>
-      <c r="F89" s="3">
-        <v>700</v>
       </c>
       <c r="G89" s="3">
         <v>700</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>900</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-700</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,28 +5275,29 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>5</v>
+      <c r="G91" s="3">
+        <v>0</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -5097,25 +5318,28 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,28 +5459,31 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
@@ -5262,37 +5492,40 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>400</v>
-      </c>
-      <c r="S94" s="3">
-        <v>200</v>
       </c>
       <c r="T94" s="3">
         <v>200</v>
       </c>
       <c r="U94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5346,8 +5580,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,67 +5793,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E100" s="3">
         <v>3500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9700</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-500</v>
       </c>
       <c r="G100" s="3">
         <v>-500</v>
       </c>
       <c r="H100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I100" s="3">
         <v>400</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-400</v>
       </c>
       <c r="J100" s="3">
         <v>-400</v>
       </c>
       <c r="K100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5641,8 +5890,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5668,63 +5917,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E102" s="3">
         <v>1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
   <si>
     <t>CTM</t>
   </si>
@@ -656,302 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E8" s="3">
         <v>14600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10000</v>
-      </c>
-      <c r="P8" s="3">
-        <v>11100</v>
       </c>
       <c r="Q8" s="3">
         <v>11100</v>
       </c>
       <c r="R8" s="3">
+        <v>11100</v>
+      </c>
+      <c r="S8" s="3">
         <v>10000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4000</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E9" s="3">
         <v>9100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6700</v>
-      </c>
-      <c r="I9" s="3">
-        <v>6800</v>
       </c>
       <c r="J9" s="3">
         <v>6800</v>
       </c>
       <c r="K9" s="3">
+        <v>6800</v>
+      </c>
+      <c r="L9" s="3">
         <v>6500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7300</v>
-      </c>
-      <c r="N9" s="3">
-        <v>5900</v>
       </c>
       <c r="O9" s="3">
         <v>5900</v>
       </c>
       <c r="P9" s="3">
+        <v>5900</v>
+      </c>
+      <c r="Q9" s="3">
         <v>6500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2200</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E10" s="3">
         <v>5500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3100</v>
-      </c>
-      <c r="U10" s="3">
-        <v>1800</v>
       </c>
       <c r="V10" s="3">
         <v>1800</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1040,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1119,50 +1138,50 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>900</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>5</v>
@@ -1170,8 +1189,11 @@
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1185,10 +1207,10 @@
         <v>400</v>
       </c>
       <c r="G15" s="3">
+        <v>400</v>
+      </c>
+      <c r="H15" s="3">
         <v>500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>600</v>
       </c>
       <c r="I15" s="3">
         <v>600</v>
@@ -1197,7 +1219,7 @@
         <v>600</v>
       </c>
       <c r="K15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="L15" s="3">
         <v>700</v>
@@ -1206,11 +1228,11 @@
         <v>700</v>
       </c>
       <c r="N15" s="3">
+        <v>700</v>
+      </c>
+      <c r="O15" s="3">
         <v>500</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1226,8 +1248,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>5</v>
@@ -1235,8 +1257,11 @@
       <c r="W15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E17" s="3">
         <v>14200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>12000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E18" s="3">
         <v>400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2700</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1700</v>
       </c>
       <c r="L18" s="3">
         <v>-1700</v>
       </c>
       <c r="M18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="N18" s="3">
         <v>-1800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4600</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-500</v>
       </c>
       <c r="V18" s="3">
         <v>-500</v>
       </c>
       <c r="W18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X18" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,56 +1444,57 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
-        <v>800</v>
-      </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-600</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1477,78 +1510,84 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E21" s="3">
         <v>800</v>
       </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-2000</v>
       </c>
-      <c r="H21" s="3">
-        <v>-800</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
@@ -1557,46 +1596,46 @@
         <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I22" s="3">
         <v>200</v>
       </c>
       <c r="J22" s="3">
+        <v>200</v>
+      </c>
+      <c r="K22" s="3">
         <v>500</v>
-      </c>
-      <c r="K22" s="3">
-        <v>800</v>
       </c>
       <c r="L22" s="3">
         <v>800</v>
       </c>
       <c r="M22" s="3">
+        <v>800</v>
+      </c>
+      <c r="N22" s="3">
         <v>1200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>900</v>
-      </c>
-      <c r="R22" s="3">
-        <v>700</v>
       </c>
       <c r="S22" s="3">
         <v>700</v>
       </c>
       <c r="T22" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="U22" s="3">
         <v>600</v>
@@ -1605,75 +1644,81 @@
         <v>600</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E23" s="3">
         <v>500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5200</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-1100</v>
       </c>
       <c r="V23" s="3">
         <v>-1100</v>
       </c>
       <c r="W23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X23" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1681,52 +1726,52 @@
         <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>100</v>
       </c>
       <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
         <v>-300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>100</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
       </c>
       <c r="K24" s="3">
+        <v>100</v>
+      </c>
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-1200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1800</v>
-      </c>
-      <c r="T24" s="3">
-        <v>-300</v>
       </c>
       <c r="U24" s="3">
         <v>-300</v>
@@ -1734,11 +1779,14 @@
       <c r="V24" s="3">
         <v>-300</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
         <v>400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4900</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-800</v>
       </c>
       <c r="V26" s="3">
         <v>-800</v>
       </c>
       <c r="W26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E27" s="3">
         <v>400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4900</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-800</v>
       </c>
       <c r="V27" s="3">
         <v>-800</v>
       </c>
       <c r="W27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,56 +2258,59 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
-        <v>-800</v>
-      </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>600</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2257,73 +2326,79 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E33" s="3">
         <v>400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4900</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-800</v>
       </c>
       <c r="V33" s="3">
         <v>-800</v>
       </c>
       <c r="W33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E35" s="3">
         <v>400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4900</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-800</v>
       </c>
       <c r="V35" s="3">
         <v>-800</v>
       </c>
       <c r="W35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,59 +2657,60 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E41" s="3">
         <v>17800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>13300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2300</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
         <v>0</v>
       </c>
@@ -2634,11 +2720,14 @@
       <c r="V41" s="3">
         <v>0</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,73 +2791,79 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E43" s="3">
         <v>9900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5800</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2805,8 +2900,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2818,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="S44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T44" s="3">
         <v>100</v>
@@ -2829,11 +2924,14 @@
       <c r="V44" s="3">
         <v>100</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>100</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2841,50 +2939,50 @@
         <v>200</v>
       </c>
       <c r="E45" s="3">
+        <v>200</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
-      </c>
-      <c r="P45" s="3">
-        <v>300</v>
       </c>
       <c r="Q45" s="3">
         <v>300</v>
       </c>
       <c r="R45" s="3">
+        <v>300</v>
+      </c>
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2897,58 +2995,61 @@
       <c r="W45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E46" s="3">
         <v>28600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8300</v>
-      </c>
-      <c r="S46" s="3">
-        <v>100</v>
       </c>
       <c r="T46" s="3">
         <v>100</v>
@@ -2959,19 +3060,22 @@
       <c r="V46" s="3">
         <v>100</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>100</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3">
         <v>100</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F47" s="3">
         <v>100</v>
@@ -2985,8 +3089,8 @@
       <c r="I47" s="3">
         <v>100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
+      <c r="J47" s="3">
+        <v>100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
@@ -3003,8 +3107,8 @@
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3027,16 +3131,19 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1100</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1200</v>
       </c>
       <c r="F48" s="3">
         <v>1200</v>
@@ -3045,31 +3152,31 @@
         <v>1200</v>
       </c>
       <c r="H48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I48" s="3">
         <v>1300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>200</v>
-      </c>
-      <c r="P48" s="3">
-        <v>300</v>
       </c>
       <c r="Q48" s="3">
         <v>300</v>
@@ -3078,73 +3185,76 @@
         <v>300</v>
       </c>
       <c r="S48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3">
         <v>100</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
       <c r="V48" s="3">
+        <v>0</v>
+      </c>
+      <c r="W48" s="3">
         <v>600</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E49" s="3">
         <v>16400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>20300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>27600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>28200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>22200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>22700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>23200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>20900</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3157,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,8 +3403,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3302,13 +3421,13 @@
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
+      <c r="I52" s="3">
+        <v>200</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
@@ -3325,8 +3444,8 @@
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -3335,11 +3454,11 @@
         <v>0</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>800</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3352,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E54" s="3">
         <v>46300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>43400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>41100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>37800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>30500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>30100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>31500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>40000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>33600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>33400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>30300</v>
-      </c>
-      <c r="S54" s="3">
-        <v>200</v>
       </c>
       <c r="T54" s="3">
         <v>200</v>
       </c>
       <c r="U54" s="3">
+        <v>200</v>
+      </c>
+      <c r="V54" s="3">
         <v>100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>700</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,90 +3661,94 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1000</v>
       </c>
       <c r="I57" s="3">
         <v>1000</v>
       </c>
       <c r="J57" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="K57" s="3">
         <v>800</v>
       </c>
       <c r="L57" s="3">
+        <v>800</v>
+      </c>
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
-      </c>
-      <c r="O57" s="3">
-        <v>1600</v>
       </c>
       <c r="P57" s="3">
         <v>1600</v>
       </c>
       <c r="Q57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>700</v>
-      </c>
-      <c r="S57" s="3">
-        <v>200</v>
       </c>
       <c r="T57" s="3">
         <v>200</v>
       </c>
       <c r="U57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
         <v>600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3800</v>
-      </c>
-      <c r="H58" s="3">
-        <v>3100</v>
       </c>
       <c r="I58" s="3">
         <v>3100</v>
@@ -3627,28 +3760,28 @@
         <v>3100</v>
       </c>
       <c r="L58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M58" s="3">
         <v>11000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2600</v>
-      </c>
-      <c r="O58" s="3">
-        <v>2300</v>
       </c>
       <c r="P58" s="3">
         <v>2300</v>
       </c>
       <c r="Q58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R58" s="3">
         <v>1400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1300</v>
-      </c>
-      <c r="S58" s="3">
-        <v>300</v>
       </c>
       <c r="T58" s="3">
         <v>300</v>
@@ -3657,131 +3790,137 @@
         <v>300</v>
       </c>
       <c r="V58" s="3">
+        <v>300</v>
+      </c>
+      <c r="W58" s="3">
         <v>400</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>300</v>
+      </c>
+      <c r="E59" s="3">
         <v>500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>900</v>
       </c>
       <c r="J59" s="3">
         <v>900</v>
       </c>
       <c r="K59" s="3">
+        <v>900</v>
+      </c>
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2900</v>
-      </c>
-      <c r="S59" s="3">
-        <v>200</v>
       </c>
       <c r="T59" s="3">
         <v>200</v>
       </c>
       <c r="U59" s="3">
+        <v>200</v>
+      </c>
+      <c r="V59" s="3">
         <v>300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>200</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E60" s="3">
         <v>6900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9800</v>
-      </c>
-      <c r="H60" s="3">
-        <v>8400</v>
       </c>
       <c r="I60" s="3">
         <v>8400</v>
       </c>
       <c r="J60" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K60" s="3">
         <v>8300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>700</v>
-      </c>
-      <c r="T60" s="3">
-        <v>600</v>
       </c>
       <c r="U60" s="3">
         <v>600</v>
@@ -3789,61 +3928,64 @@
       <c r="V60" s="3">
         <v>600</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>600</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8900</v>
-      </c>
-      <c r="N61" s="3">
-        <v>7700</v>
       </c>
       <c r="O61" s="3">
         <v>7700</v>
       </c>
       <c r="P61" s="3">
+        <v>7700</v>
+      </c>
+      <c r="Q61" s="3">
         <v>7600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10500</v>
-      </c>
-      <c r="S61" s="3">
-        <v>300</v>
       </c>
       <c r="T61" s="3">
         <v>300</v>
@@ -3852,13 +3994,16 @@
         <v>300</v>
       </c>
       <c r="V61" s="3">
+        <v>300</v>
+      </c>
+      <c r="W61" s="3">
         <v>200</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3868,26 +4013,26 @@
       <c r="E62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>200</v>
       </c>
       <c r="I62" s="3">
         <v>200</v>
       </c>
       <c r="J62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
+      <c r="L62" s="3">
+        <v>300</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>5</v>
@@ -3895,8 +4040,8 @@
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -3907,8 +4052,8 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>5</v>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>5</v>
@@ -3922,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E66" s="3">
         <v>9500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17200</v>
-      </c>
-      <c r="L66" s="3">
-        <v>17700</v>
       </c>
       <c r="M66" s="3">
         <v>17700</v>
       </c>
       <c r="N66" s="3">
+        <v>17700</v>
+      </c>
+      <c r="O66" s="3">
         <v>17100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1000</v>
-      </c>
-      <c r="T66" s="3">
-        <v>900</v>
       </c>
       <c r="U66" s="3">
         <v>900</v>
       </c>
       <c r="V66" s="3">
+        <v>900</v>
+      </c>
+      <c r="W66" s="3">
         <v>800</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-56600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-55200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-55600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-55300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-54100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-51300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-50000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-48100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-44000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-41800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-32600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-30400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-26100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-20400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-17200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-12500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1900</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E76" s="3">
         <v>36700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>31800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-900</v>
-      </c>
-      <c r="T76" s="3">
-        <v>-800</v>
       </c>
       <c r="U76" s="3">
         <v>-800</v>
       </c>
       <c r="V76" s="3">
+        <v>-800</v>
+      </c>
+      <c r="W76" s="3">
         <v>-100</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E81" s="3">
         <v>400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4900</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-800</v>
       </c>
       <c r="V81" s="3">
         <v>-800</v>
       </c>
       <c r="W81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5056,7 +5254,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="P83" s="3">
         <v>500</v>
@@ -5068,10 +5266,10 @@
         <v>500</v>
       </c>
       <c r="S83" s="3">
+        <v>500</v>
+      </c>
+      <c r="T83" s="3">
         <v>800</v>
-      </c>
-      <c r="T83" s="3">
-        <v>400</v>
       </c>
       <c r="U83" s="3">
         <v>400</v>
@@ -5080,10 +5278,13 @@
         <v>400</v>
       </c>
       <c r="W83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-400</v>
-      </c>
-      <c r="H89" s="3">
-        <v>700</v>
       </c>
       <c r="I89" s="3">
         <v>700</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>900</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-700</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,8 +5716,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5506,25 +5726,25 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>5</v>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5545,25 +5765,28 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,34 +5918,37 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -5728,37 +5957,40 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>400</v>
-      </c>
-      <c r="U94" s="3">
-        <v>200</v>
       </c>
       <c r="V94" s="3">
         <v>200</v>
       </c>
       <c r="W94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5820,8 +6053,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5847,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E100" s="3">
         <v>2100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9700</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-500</v>
       </c>
       <c r="I100" s="3">
         <v>-500</v>
       </c>
       <c r="J100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K100" s="3">
         <v>400</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-400</v>
       </c>
       <c r="L100" s="3">
         <v>-400</v>
       </c>
       <c r="M100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6145,8 +6393,8 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6172,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E102" s="3">
         <v>3100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>0</v>
       </c>
     </row>
